--- a/centrality_report.xlsx
+++ b/centrality_report.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Центральности_группы" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Топология_сети (V и E)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,7 +435,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Количество связей (Degree)</t>
+          <t>Количество граней / связей (Degree)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -455,110 +456,565 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>181840990</v>
+        <v>422397933</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Сайын Кужугет</t>
+          <t>Андрей Клейменов</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://vk.com/toorudeboy</t>
+          <t>https://vk.com/id422397933</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>332</v>
+        <v>5000</v>
       </c>
       <c r="E2" t="n">
-        <v>0.710982</v>
+        <v>0.5510699999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.405951</v>
+        <v>0.530338</v>
       </c>
       <c r="G2" t="n">
-        <v>0.651782</v>
+        <v>0.13955</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>677045683</v>
+        <v>181840990</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Руслан Аллабергенов</t>
+          <t>Сайын Кужугет</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://vk.com/rskator</t>
+          <t>https://vk.com/toorudeboy</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>108</v>
+        <v>624</v>
       </c>
       <c r="E3" t="n">
-        <v>0.168352</v>
+        <v>0.041008</v>
       </c>
       <c r="F3" t="n">
-        <v>0.265589</v>
+        <v>0.395088</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004478</v>
+        <v>0.023555</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>236434667</v>
+        <v>354792455</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Александр Голоктионов</t>
+          <t>Сергей Абрамов</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://vk.com/dedvnutree</t>
+          <t>https://vk.com/s.abramov2</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>134</v>
+        <v>713</v>
       </c>
       <c r="E4" t="n">
-        <v>0.14754</v>
+        <v>0.039195</v>
       </c>
       <c r="F4" t="n">
-        <v>0.29987</v>
+        <v>0.361982</v>
       </c>
       <c r="G4" t="n">
-        <v>0.019921</v>
+        <v>0.044587</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>392942223</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ruslän Dächev</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://vk.com/fulliener</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>210</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.021492</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.29197</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001203</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>236434667</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Александр Голоктионов</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://vk.com/dedvnutree</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>235</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.012998</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.394731</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.015877</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>708207289</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ле Хиеп-Хый</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://vk.com/antonlevn</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>111</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.011946</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.246396</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.000275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>278508214</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Илья Руднев</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://vk.com/rudnev911</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>227</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.01192</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.331551</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.009148</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133821410</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Кирилл Дренин</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://vk.com/freezefinn</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>127</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.011686</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.314271</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.00228</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>214576903</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Артем Кузьмин</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://vk.com/metonimiaa</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>126</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.010462</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.317703</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001555</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>677045683</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Руслан Аллабергенов</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://vk.com/rskator</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>177</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.010453</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.306315</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001394</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>147436715</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Мария Александрова</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://vk.com/kotletosss</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>112</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.01039</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.308846</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.003965</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>241970575</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Никита Марков</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://vk.com/1nkarat</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>87</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.006844</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.305718</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.00346</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>172152768</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Сергей Федькин</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://vk.com/fed_serega</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>62</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.005821</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.284424</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.000695</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>301455650</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Илья Бурмистров</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://vk.com/ogponcha</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>60</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.00496</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.280877</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.000262</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>437474057</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Дмитрий Базлов</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>https://vk.com/dimabazlov</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>40</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.084551</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.290579</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.023229</v>
+      <c r="D16" t="n">
+        <v>102</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.002629</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.361205</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005393</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>229017385</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Кирилл Кучеренко</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://vk.com/daioru</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.002572</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.349666</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.001842</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>830638754</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Клим Волохов</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://vk.com/id830638754</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.001742</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.282315</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.000515</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>193511426</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Александр Васильев</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://vk.com/gs1ayer</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>80</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.000193</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.367733</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.016824</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1098513955</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Дмитрий Ядовитый</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://vk.com/id1098513955</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5.4e-05</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Количество точек (вершин |V|)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Количество граней (рёбер |E|)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Плотность графа (Density)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Среднее число связей (Avg Degree)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>18360</v>
+      </c>
+      <c r="B2" t="n">
+        <v>120283</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.000714</v>
+      </c>
+      <c r="D2" t="n">
+        <v>13.1</v>
       </c>
     </row>
   </sheetData>
